--- a/salidas/empresas/APA.xlsx
+++ b/salidas/empresas/APA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>52.92542266845703</v>
+        <v>52.92543411254883</v>
       </c>
       <c r="C2" t="n">
         <v>75.52999877929688</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>46.8922233581543</v>
+        <v>46.89223861694336</v>
       </c>
       <c r="C3" t="n">
         <v>66.91999816894531</v>
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>49.85018157958984</v>
+        <v>49.85017395019531</v>
       </c>
       <c r="C5" t="n">
         <v>71.04000091552734</v>
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>47.89237976074219</v>
+        <v>47.89238739013672</v>
       </c>
       <c r="C7" t="n">
         <v>68.25</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>49.52591323852539</v>
+        <v>49.52589797973633</v>
       </c>
       <c r="C8" t="n">
         <v>70.47000122070312</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>45.87836837768555</v>
+        <v>45.87838745117188</v>
       </c>
       <c r="C9" t="n">
         <v>65.27999877929688</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>44.41659164428711</v>
+        <v>44.41658782958984</v>
       </c>
       <c r="C10" t="n">
         <v>63.20000076293945</v>
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>49.25987243652344</v>
+        <v>49.2598991394043</v>
       </c>
       <c r="C12" t="n">
         <v>69.93000030517578</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>46.85078430175781</v>
+        <v>46.85076904296875</v>
       </c>
       <c r="C13" t="n">
         <v>66.51000213623047</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>51.51837539672852</v>
+        <v>51.51839065551758</v>
       </c>
       <c r="C14" t="n">
         <v>72.97000122070312</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>48.334228515625</v>
+        <v>48.3342170715332</v>
       </c>
       <c r="C15" t="n">
         <v>68.45999908447266</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>49.91571426391602</v>
+        <v>49.91570663452148</v>
       </c>
       <c r="C16" t="n">
         <v>70.69999694824219</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>51.28941345214844</v>
+        <v>51.28940200805664</v>
       </c>
       <c r="C17" t="n">
         <v>72.5</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>57.12580108642578</v>
+        <v>57.12575531005859</v>
       </c>
       <c r="C18" t="n">
         <v>80.75</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>57.72001266479492</v>
+        <v>57.72003173828125</v>
       </c>
       <c r="C19" t="n">
         <v>81.58999633789062</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>57.28756332397461</v>
+        <v>57.28753280639648</v>
       </c>
       <c r="C20" t="n">
         <v>80.83999633789062</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>54.83559417724609</v>
+        <v>54.83560180664062</v>
       </c>
       <c r="C21" t="n">
         <v>77.37999725341797</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>63.82133483886719</v>
+        <v>63.82132339477539</v>
       </c>
       <c r="C22" t="n">
         <v>90.05999755859375</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>73.68099212646484</v>
+        <v>73.68097686767578</v>
       </c>
       <c r="C23" t="n">
         <v>103.8099975585938</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>68.69841003417969</v>
+        <v>68.69843292236328</v>
       </c>
       <c r="C24" t="n">
         <v>96.79000091552734</v>
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>67.78547668457031</v>
+        <v>67.78549957275391</v>
       </c>
       <c r="C26" t="n">
         <v>95.36000061035156</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>81.61521911621094</v>
+        <v>81.61522674560547</v>
       </c>
       <c r="C27" t="n">
         <v>114.7099990844727</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>85.96242523193359</v>
+        <v>85.96240997314453</v>
       </c>
       <c r="C28" t="n">
         <v>120.8199996948242</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>95.92716979980469</v>
+        <v>95.92720794677734</v>
       </c>
       <c r="C29" t="n">
         <v>134.6799926757812</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>95.48561859130859</v>
+        <v>95.485595703125</v>
       </c>
       <c r="C30" t="n">
         <v>134.0599975585938</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>99.00417327880859</v>
+        <v>99.00418090820312</v>
       </c>
       <c r="C31" t="n">
         <v>139</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>80.00221252441406</v>
+        <v>80.00222778320312</v>
       </c>
       <c r="C32" t="n">
         <v>112.1699981689453</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>81.57844543457031</v>
+        <v>81.57848358154297</v>
       </c>
       <c r="C33" t="n">
         <v>114.379997253418</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>74.37491607666016</v>
+        <v>74.37490081787109</v>
       </c>
       <c r="C34" t="n">
         <v>104.2799987792969</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>58.83913803100586</v>
+        <v>58.83910369873047</v>
       </c>
       <c r="C35" t="n">
         <v>82.33000183105469</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>55.24428176879883</v>
+        <v>55.24432373046875</v>
       </c>
       <c r="C36" t="n">
         <v>77.30000305175781</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>53.26466751098633</v>
+        <v>53.26466369628906</v>
       </c>
       <c r="C37" t="n">
         <v>74.52999877929688</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>53.70871353149414</v>
+        <v>53.70869445800781</v>
       </c>
       <c r="C38" t="n">
         <v>75</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>42.31530380249023</v>
+        <v>42.31531524658203</v>
       </c>
       <c r="C39" t="n">
         <v>59.09000015258789</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>45.89587783813477</v>
+        <v>45.89587020874023</v>
       </c>
       <c r="C40" t="n">
         <v>64.08999633789062</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>52.28973007202148</v>
+        <v>52.28976440429688</v>
       </c>
       <c r="C41" t="n">
         <v>72.86000061035156</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>60.47122192382812</v>
+        <v>60.47124862670898</v>
       </c>
       <c r="C42" t="n">
         <v>84.26000213623047</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>51.78019332885742</v>
+        <v>51.78020858764648</v>
       </c>
       <c r="C43" t="n">
         <v>72.15000152587891</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>60.36867523193359</v>
+        <v>60.36869812011719</v>
       </c>
       <c r="C44" t="n">
         <v>83.94999694824219</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>61.08779907226562</v>
+        <v>61.08777618408203</v>
       </c>
       <c r="C45" t="n">
         <v>84.94999694824219</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>66.03522491455078</v>
+        <v>66.03520965576172</v>
       </c>
       <c r="C46" t="n">
         <v>91.83000183105469</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>67.7796630859375</v>
+        <v>67.77964782714844</v>
       </c>
       <c r="C47" t="n">
         <v>94.12000274658203</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>68.61505126953125</v>
+        <v>68.61504364013672</v>
       </c>
       <c r="C48" t="n">
         <v>95.27999877929688</v>
@@ -1375,7 +1387,7 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1394,11 +1406,11 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>71.22692108154297</v>
+        <v>71.22689819335938</v>
       </c>
       <c r="C50" t="n">
         <v>98.76999664306641</v>
@@ -1413,11 +1425,11 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>74.73881530761719</v>
+        <v>74.73884582519531</v>
       </c>
       <c r="C51" t="n">
         <v>103.6399993896484</v>
@@ -1432,11 +1444,11 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>73.19560241699219</v>
+        <v>73.19558715820312</v>
       </c>
       <c r="C52" t="n">
         <v>101.5</v>
@@ -1451,11 +1463,11 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>73.48787689208984</v>
+        <v>73.48789215087891</v>
       </c>
       <c r="C53" t="n">
         <v>101.7600021362305</v>
@@ -1470,11 +1482,11 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>64.66299438476562</v>
+        <v>64.66300201416016</v>
       </c>
       <c r="C54" t="n">
         <v>89.54000091552734</v>
@@ -1489,11 +1501,11 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>60.79938125610352</v>
+        <v>60.79937362670898</v>
       </c>
       <c r="C55" t="n">
         <v>84.19000244140625</v>
@@ -1508,11 +1520,11 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>69.14606475830078</v>
+        <v>69.14608001708984</v>
       </c>
       <c r="C56" t="n">
         <v>95.58000183105469</v>
@@ -1527,7 +1539,7 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1546,11 +1558,11 @@
       <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>70.72316741943359</v>
+        <v>70.72315979003906</v>
       </c>
       <c r="C58" t="n">
         <v>97.76000213623047</v>
@@ -1565,11 +1577,11 @@
       <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>73.18891906738281</v>
+        <v>73.18889617919922</v>
       </c>
       <c r="C59" t="n">
         <v>101.0199966430664</v>
@@ -1584,11 +1596,11 @@
       <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>77.98509979248047</v>
+        <v>77.98508453369141</v>
       </c>
       <c r="C60" t="n">
         <v>107.6399993896484</v>
@@ -1603,11 +1615,11 @@
       <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>86.38202667236328</v>
+        <v>86.38204956054688</v>
       </c>
       <c r="C61" t="n">
         <v>119.2300033569336</v>
@@ -1622,7 +1634,7 @@
       <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1641,11 +1653,11 @@
       <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>90.39337921142578</v>
+        <v>90.39339447021484</v>
       </c>
       <c r="C63" t="n">
         <v>124.620002746582</v>
@@ -1660,11 +1672,11 @@
       <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>94.96307373046875</v>
+        <v>94.96308898925781</v>
       </c>
       <c r="C64" t="n">
         <v>130.9199981689453</v>
@@ -1679,11 +1691,11 @@
       <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>96.86035919189453</v>
+        <v>96.86038970947266</v>
       </c>
       <c r="C65" t="n">
         <v>133.3699951171875</v>
@@ -1698,11 +1710,11 @@
       <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>90.49114227294922</v>
+        <v>90.49110412597656</v>
       </c>
       <c r="C66" t="n">
         <v>124.5999984741211</v>
@@ -1717,11 +1729,11 @@
       <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>89.61233520507812</v>
+        <v>89.61234283447266</v>
       </c>
       <c r="C67" t="n">
         <v>123.3899993896484</v>
@@ -1736,11 +1748,11 @@
       <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>89.95933532714844</v>
+        <v>89.95932769775391</v>
       </c>
       <c r="C68" t="n">
         <v>123.7200012207031</v>
@@ -1755,7 +1767,7 @@
       <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1774,11 +1786,11 @@
       <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>58.34413146972656</v>
+        <v>58.34414291381836</v>
       </c>
       <c r="C70" t="n">
         <v>80.23999786376953</v>
@@ -1793,7 +1805,7 @@
       <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -1812,11 +1824,11 @@
       <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>72.42501068115234</v>
+        <v>72.42500305175781</v>
       </c>
       <c r="C72" t="n">
         <v>99.44000244140625</v>
@@ -1831,7 +1843,7 @@
       <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -1850,11 +1862,11 @@
       <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>72.13053131103516</v>
+        <v>72.13052368164062</v>
       </c>
       <c r="C74" t="n">
         <v>98.87999725341797</v>
@@ -1869,11 +1881,11 @@
       <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>78.73227691650391</v>
+        <v>78.73226165771484</v>
       </c>
       <c r="C75" t="n">
         <v>107.9300003051758</v>
@@ -1888,11 +1900,11 @@
       <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>73.26850891113281</v>
+        <v>73.26849365234375</v>
       </c>
       <c r="C76" t="n">
         <v>100.4400024414062</v>
@@ -1907,7 +1919,7 @@
       <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -1926,11 +1938,11 @@
       <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>59.47424697875977</v>
+        <v>59.47425079345703</v>
       </c>
       <c r="C78" t="n">
         <v>81.37999725341797</v>
@@ -1945,11 +1957,11 @@
       <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>64.23189544677734</v>
+        <v>64.23188781738281</v>
       </c>
       <c r="C79" t="n">
         <v>87.88999938964844</v>
@@ -1964,11 +1976,11 @@
       <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>63.06346893310547</v>
+        <v>63.06345367431641</v>
       </c>
       <c r="C80" t="n">
         <v>86.12000274658203</v>
@@ -1983,11 +1995,11 @@
       <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>62.79252243041992</v>
+        <v>62.79251480102539</v>
       </c>
       <c r="C81" t="n">
         <v>85.75</v>
@@ -2002,11 +2014,11 @@
       <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>63.31976318359375</v>
+        <v>63.31975173950195</v>
       </c>
       <c r="C82" t="n">
         <v>86.47000122070312</v>
@@ -2021,11 +2033,11 @@
       <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>60.69002532958984</v>
+        <v>60.69001770019531</v>
       </c>
       <c r="C83" t="n">
         <v>82.72000122070312</v>
@@ -2040,11 +2052,11 @@
       <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>56.55938339233398</v>
+        <v>56.55936813354492</v>
       </c>
       <c r="C84" t="n">
         <v>77.08999633789062</v>
@@ -2059,11 +2071,11 @@
       <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>57.59387969970703</v>
+        <v>57.59389495849609</v>
       </c>
       <c r="C85" t="n">
         <v>78.5</v>
@@ -2078,11 +2090,11 @@
       <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>61.58255767822266</v>
+        <v>61.58256149291992</v>
       </c>
       <c r="C86" t="n">
         <v>83.76000213623047</v>
@@ -2097,11 +2109,11 @@
       <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>54.60526275634766</v>
+        <v>54.60525512695312</v>
       </c>
       <c r="C87" t="n">
         <v>74.26999664306641</v>
@@ -2116,11 +2128,11 @@
       <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>56.73005676269531</v>
+        <v>56.73006439208984</v>
       </c>
       <c r="C88" t="n">
         <v>77.16000366210938</v>
@@ -2135,11 +2147,11 @@
       <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>54.47099304199219</v>
+        <v>54.47097396850586</v>
       </c>
       <c r="C89" t="n">
         <v>73.87999725341797</v>
@@ -2154,11 +2166,11 @@
       <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>60.55363845825195</v>
+        <v>60.55363464355469</v>
       </c>
       <c r="C90" t="n">
         <v>82.12999725341797</v>
@@ -2173,7 +2185,7 @@
       <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2192,11 +2204,11 @@
       <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>59.31130218505859</v>
+        <v>59.3112907409668</v>
       </c>
       <c r="C92" t="n">
         <v>80.25</v>
@@ -2211,7 +2223,7 @@
       <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2230,11 +2242,11 @@
       <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>62.9254264831543</v>
+        <v>62.92541122436523</v>
       </c>
       <c r="C94" t="n">
         <v>85.13999938964844</v>
@@ -2249,11 +2261,11 @@
       <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>65.77570343017578</v>
+        <v>65.77568054199219</v>
       </c>
       <c r="C95" t="n">
         <v>88.80000305175781</v>
@@ -2268,7 +2280,7 @@
       <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2287,11 +2299,11 @@
       <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>63.6572380065918</v>
+        <v>63.65723419189453</v>
       </c>
       <c r="C97" t="n">
         <v>85.94000244140625</v>
@@ -2306,7 +2318,7 @@
       <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2325,11 +2337,11 @@
       <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>58.86852264404297</v>
+        <v>58.86854934692383</v>
       </c>
       <c r="C99" t="n">
         <v>79.29000091552734</v>
@@ -2344,11 +2356,11 @@
       <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>61.58588790893555</v>
+        <v>61.58585357666016</v>
       </c>
       <c r="C100" t="n">
         <v>82.94999694824219</v>
@@ -2363,7 +2375,7 @@
       <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2382,11 +2394,11 @@
       <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>69.41697692871094</v>
+        <v>69.41698455810547</v>
       </c>
       <c r="C102" t="n">
         <v>93.22000122070312</v>
@@ -2401,11 +2413,11 @@
       <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>74.92743682861328</v>
+        <v>74.92744445800781</v>
       </c>
       <c r="C103" t="n">
         <v>100.620002746582</v>
@@ -2420,7 +2432,7 @@
       <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2439,11 +2451,11 @@
       <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>76.0206298828125</v>
+        <v>76.02062225341797</v>
       </c>
       <c r="C105" t="n">
         <v>101.8300018310547</v>
@@ -2458,11 +2470,11 @@
       <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>70.07814788818359</v>
+        <v>70.07814025878906</v>
       </c>
       <c r="C106" t="n">
         <v>93.87000274658203</v>
@@ -2477,11 +2489,11 @@
       <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>57.83168029785156</v>
+        <v>57.83169937133789</v>
       </c>
       <c r="C107" t="n">
         <v>77.19999694824219</v>
@@ -2496,11 +2508,11 @@
       <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>48.01080322265625</v>
+        <v>48.01079177856445</v>
       </c>
       <c r="C108" t="n">
         <v>64.08999633789062</v>
@@ -2515,11 +2527,11 @@
       <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>46.94704818725586</v>
+        <v>46.94704437255859</v>
       </c>
       <c r="C109" t="n">
         <v>62.66999816894531</v>
@@ -2534,11 +2546,11 @@
       <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>47.06115341186523</v>
+        <v>47.0611572265625</v>
       </c>
       <c r="C110" t="n">
         <v>62.56999969482422</v>
@@ -2553,11 +2565,11 @@
       <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>49.52061080932617</v>
+        <v>49.52061462402344</v>
       </c>
       <c r="C111" t="n">
         <v>65.83999633789062</v>
@@ -2572,11 +2584,11 @@
       <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>45.37636566162109</v>
+        <v>45.37636947631836</v>
       </c>
       <c r="C112" t="n">
         <v>60.33000183105469</v>
@@ -2591,11 +2603,11 @@
       <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>51.62949752807617</v>
+        <v>51.6295051574707</v>
       </c>
       <c r="C113" t="n">
         <v>68.40000152587891</v>
@@ -2610,11 +2622,11 @@
       <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>45.16826629638672</v>
+        <v>45.16825485229492</v>
       </c>
       <c r="C114" t="n">
         <v>59.84000015258789</v>
@@ -2629,11 +2641,11 @@
       <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>43.50010299682617</v>
+        <v>43.50010681152344</v>
       </c>
       <c r="C115" t="n">
         <v>57.63000106811523</v>
@@ -2648,11 +2660,11 @@
       <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>34.78765869140625</v>
+        <v>34.78765487670898</v>
       </c>
       <c r="C116" t="n">
         <v>45.86000061035156</v>
@@ -2667,11 +2679,11 @@
       <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>34.31734848022461</v>
+        <v>34.31734085083008</v>
       </c>
       <c r="C117" t="n">
         <v>45.2400016784668</v>
@@ -2686,11 +2698,11 @@
       <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>29.70529937744141</v>
+        <v>29.70529174804688</v>
       </c>
       <c r="C118" t="n">
         <v>39.15999984741211</v>
@@ -2705,11 +2717,11 @@
       <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>35.94929504394531</v>
+        <v>35.94927978515625</v>
       </c>
       <c r="C119" t="n">
         <v>47.13000106811523</v>
@@ -2724,11 +2736,11 @@
       <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>37.51295852661133</v>
+        <v>37.51296234130859</v>
       </c>
       <c r="C120" t="n">
         <v>49.18000030517578</v>
@@ -2743,11 +2755,11 @@
       <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>33.92033386230469</v>
+        <v>33.92032623291016</v>
       </c>
       <c r="C121" t="n">
         <v>44.47000122070312</v>
@@ -2762,11 +2774,11 @@
       <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>32.68516540527344</v>
+        <v>32.6851806640625</v>
       </c>
       <c r="C122" t="n">
         <v>42.54000091552734</v>
@@ -2781,11 +2793,11 @@
       <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>29.41205596923828</v>
+        <v>29.41204452514648</v>
       </c>
       <c r="C123" t="n">
         <v>38.27999877929688</v>
@@ -2800,11 +2812,11 @@
       <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>37.50266265869141</v>
+        <v>37.50265502929688</v>
       </c>
       <c r="C124" t="n">
         <v>48.81000137329102</v>
@@ -2819,11 +2831,11 @@
       <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>41.98846435546875</v>
+        <v>41.98845672607422</v>
       </c>
       <c r="C125" t="n">
         <v>54.40000152587891</v>
@@ -2838,11 +2850,11 @@
       <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>44.10332870483398</v>
+        <v>44.10332489013672</v>
       </c>
       <c r="C126" t="n">
         <v>57.13999938964844</v>
@@ -2857,11 +2869,11 @@
       <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>42.96871566772461</v>
+        <v>42.96871185302734</v>
       </c>
       <c r="C127" t="n">
         <v>55.66999816894531</v>
@@ -2876,11 +2888,11 @@
       <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>40.70661926269531</v>
+        <v>40.70662307739258</v>
       </c>
       <c r="C128" t="n">
         <v>52.5</v>
@@ -2895,11 +2907,11 @@
       <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>38.53559875488281</v>
+        <v>38.53560638427734</v>
       </c>
       <c r="C129" t="n">
         <v>49.70000076293945</v>
@@ -2914,7 +2926,7 @@
       <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -2933,11 +2945,11 @@
       <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>46.30290222167969</v>
+        <v>46.30289840698242</v>
       </c>
       <c r="C131" t="n">
         <v>59.47999954223633</v>
@@ -2952,11 +2964,11 @@
       <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>51.33955001831055</v>
+        <v>51.33953857421875</v>
       </c>
       <c r="C132" t="n">
         <v>65.94999694824219</v>
@@ -2971,11 +2983,11 @@
       <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>49.40895843505859</v>
+        <v>49.4089469909668</v>
       </c>
       <c r="C133" t="n">
         <v>63.47000122070312</v>
@@ -2990,11 +3002,11 @@
       <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>46.75279998779297</v>
+        <v>46.75281143188477</v>
       </c>
       <c r="C134" t="n">
         <v>59.81999969482422</v>
@@ -3009,11 +3021,11 @@
       <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>41.10213851928711</v>
+        <v>41.10214233398438</v>
       </c>
       <c r="C135" t="n">
         <v>52.59000015258789</v>
@@ -3028,11 +3040,11 @@
       <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>40.16426086425781</v>
+        <v>40.16426467895508</v>
       </c>
       <c r="C136" t="n">
         <v>51.38999938964844</v>
@@ -3047,11 +3059,11 @@
       <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>38.20430374145508</v>
+        <v>38.20430755615234</v>
       </c>
       <c r="C137" t="n">
         <v>48.63999938964844</v>
@@ -3066,11 +3078,11 @@
       <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>36.7276496887207</v>
+        <v>36.72765731811523</v>
       </c>
       <c r="C138" t="n">
         <v>46.7599983215332</v>
@@ -3085,11 +3097,11 @@
       <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>37.64662933349609</v>
+        <v>37.64664077758789</v>
       </c>
       <c r="C139" t="n">
         <v>47.93000030517578</v>
@@ -3104,11 +3116,11 @@
       <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>39.06871795654297</v>
+        <v>39.06872177124023</v>
       </c>
       <c r="C140" t="n">
         <v>49.47999954223633</v>
@@ -3123,11 +3135,11 @@
       <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>30.66752815246582</v>
+        <v>30.66752433776855</v>
       </c>
       <c r="C141" t="n">
         <v>38.84000015258789</v>
@@ -3142,11 +3154,11 @@
       <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>36.16303634643555</v>
+        <v>36.16304397583008</v>
       </c>
       <c r="C142" t="n">
         <v>45.79999923706055</v>
@@ -3161,11 +3173,11 @@
       <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>32.86008071899414</v>
+        <v>32.86007308959961</v>
       </c>
       <c r="C143" t="n">
         <v>41.36999893188477</v>
@@ -3180,11 +3192,11 @@
       <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>33.22544860839844</v>
+        <v>33.22544479370117</v>
       </c>
       <c r="C144" t="n">
         <v>41.83000183105469</v>
@@ -3199,7 +3211,7 @@
       <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -3218,11 +3230,11 @@
       <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>35.83193588256836</v>
+        <v>35.83193206787109</v>
       </c>
       <c r="C146" t="n">
         <v>44.86999893188477</v>
@@ -3237,11 +3249,11 @@
       <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>27.2712345123291</v>
+        <v>27.271240234375</v>
       </c>
       <c r="C147" t="n">
         <v>34.15000152587891</v>
@@ -3256,11 +3268,11 @@
       <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>30.72905731201172</v>
+        <v>30.72905921936035</v>
       </c>
       <c r="C148" t="n">
         <v>38.47999954223633</v>
@@ -3275,11 +3287,11 @@
       <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>32.897216796875</v>
+        <v>32.89720916748047</v>
       </c>
       <c r="C149" t="n">
         <v>40.95000076293945</v>
@@ -3294,7 +3306,7 @@
       <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -3313,11 +3325,11 @@
       <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>37.55664825439453</v>
+        <v>37.55665588378906</v>
       </c>
       <c r="C151" t="n">
         <v>46.75</v>
@@ -3332,11 +3344,11 @@
       <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>37.16267776489258</v>
+        <v>37.16267013549805</v>
       </c>
       <c r="C152" t="n">
         <v>46</v>
@@ -3351,11 +3363,11 @@
       <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>35.40956115722656</v>
+        <v>35.40956497192383</v>
       </c>
       <c r="C153" t="n">
         <v>43.83000183105469</v>
@@ -3370,11 +3382,11 @@
       <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>38.51183700561523</v>
+        <v>38.51183319091797</v>
       </c>
       <c r="C154" t="n">
         <v>47.66999816894531</v>
@@ -3389,11 +3401,11 @@
       <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>30.74383926391602</v>
+        <v>30.74383735656738</v>
       </c>
       <c r="C155" t="n">
         <v>37.83000183105469</v>
@@ -3408,11 +3420,11 @@
       <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>28.5495777130127</v>
+        <v>28.54958724975586</v>
       </c>
       <c r="C156" t="n">
         <v>35.13000106811523</v>
@@ -3427,11 +3439,11 @@
       <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>21.33295631408691</v>
+        <v>21.33295249938965</v>
       </c>
       <c r="C157" t="n">
         <v>26.25</v>
@@ -3446,11 +3458,11 @@
       <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>26.88437652587891</v>
+        <v>26.88437843322754</v>
       </c>
       <c r="C158" t="n">
         <v>32.81999969482422</v>
@@ -3465,11 +3477,11 @@
       <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>27.17926788330078</v>
+        <v>27.17927169799805</v>
       </c>
       <c r="C159" t="n">
         <v>33.18000030517578</v>
@@ -3484,11 +3496,11 @@
       <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>28.3915958404541</v>
+        <v>28.3916015625</v>
       </c>
       <c r="C160" t="n">
         <v>34.65999984741211</v>
@@ -3503,11 +3515,11 @@
       <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>27.14228439331055</v>
+        <v>27.14228630065918</v>
       </c>
       <c r="C161" t="n">
         <v>32.90999984741211</v>
@@ -3522,7 +3534,7 @@
       <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -3541,7 +3553,7 @@
       <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -3560,11 +3572,11 @@
       <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>20.3563175201416</v>
+        <v>20.35631561279297</v>
       </c>
       <c r="C164" t="n">
         <v>24.42000007629395</v>
@@ -3579,7 +3591,7 @@
       <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -3598,11 +3610,11 @@
       <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>21.3399600982666</v>
+        <v>21.33995819091797</v>
       </c>
       <c r="C166" t="n">
         <v>25.60000038146973</v>
@@ -3617,11 +3629,11 @@
       <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>18.25901985168457</v>
+        <v>18.2590217590332</v>
       </c>
       <c r="C167" t="n">
         <v>21.65999984741211</v>
@@ -3636,11 +3648,11 @@
       <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>18.78167724609375</v>
+        <v>18.78167533874512</v>
       </c>
       <c r="C168" t="n">
         <v>22.28000068664551</v>
@@ -3655,11 +3667,11 @@
       <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>21.57195091247559</v>
+        <v>21.57194709777832</v>
       </c>
       <c r="C169" t="n">
         <v>25.59000015258789</v>
@@ -3674,11 +3686,11 @@
       <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>23.30983924865723</v>
+        <v>23.30984115600586</v>
       </c>
       <c r="C170" t="n">
         <v>27.44000053405762</v>
@@ -3693,11 +3705,11 @@
       <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>21.16914558410645</v>
+        <v>21.16914176940918</v>
       </c>
       <c r="C171" t="n">
         <v>24.92000007629395</v>
@@ -3712,7 +3724,7 @@
       <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -3731,11 +3743,11 @@
       <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>11.14410400390625</v>
+        <v>11.14410495758057</v>
       </c>
       <c r="C173" t="n">
         <v>13.07999992370605</v>
@@ -3750,11 +3762,11 @@
       <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>9.193035125732422</v>
+        <v>9.193037986755371</v>
       </c>
       <c r="C174" t="n">
         <v>10.78999996185303</v>
@@ -3769,7 +3781,7 @@
       <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -3788,11 +3800,11 @@
       <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>13.10222244262695</v>
+        <v>13.10222148895264</v>
       </c>
       <c r="C176" t="n">
         <v>15.35000038146973</v>
@@ -3807,11 +3819,11 @@
       <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>12.63276100158691</v>
+        <v>12.6327600479126</v>
       </c>
       <c r="C177" t="n">
         <v>14.80000019073486</v>
@@ -3826,11 +3838,11 @@
       <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>8.083258628845215</v>
+        <v>8.083256721496582</v>
       </c>
       <c r="C178" t="n">
         <v>9.470000267028809</v>
@@ -3845,11 +3857,11 @@
       <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>7.103067398071289</v>
+        <v>7.103066444396973</v>
       </c>
       <c r="C179" t="n">
         <v>8.300000190734863</v>
@@ -3864,7 +3876,7 @@
       <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -3883,7 +3895,7 @@
       <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -3902,11 +3914,11 @@
       <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>12.23820972442627</v>
+        <v>12.23821067810059</v>
       </c>
       <c r="C182" t="n">
         <v>14.27999973297119</v>
@@ -3921,7 +3933,7 @@
       <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -3940,7 +3952,7 @@
       <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -3959,7 +3971,7 @@
       <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -3978,11 +3990,11 @@
       <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>17.85221862792969</v>
+        <v>17.85222053527832</v>
       </c>
       <c r="C186" t="n">
         <v>20.79999923706055</v>
@@ -4003,7 +4015,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -4028,11 +4040,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>16.11568450927734</v>
+        <v>16.11568832397461</v>
       </c>
       <c r="C188" t="n">
         <v>18.75</v>
@@ -4053,7 +4065,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -4078,11 +4090,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>18.41915893554688</v>
+        <v>18.41916275024414</v>
       </c>
       <c r="C190" t="n">
         <v>21.43000030517578</v>
@@ -4103,7 +4115,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -4128,11 +4140,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>22.20035362243652</v>
+        <v>22.20036125183105</v>
       </c>
       <c r="C192" t="n">
         <v>25.77000045776367</v>
@@ -4153,11 +4165,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>23.16520881652832</v>
+        <v>23.16521644592285</v>
       </c>
       <c r="C193" t="n">
         <v>26.88999938964844</v>
@@ -4178,11 +4190,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>28.72064399719238</v>
+        <v>28.72064781188965</v>
       </c>
       <c r="C194" t="n">
         <v>33.20999908447266</v>
@@ -4203,11 +4215,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>30.81350898742676</v>
+        <v>30.81350708007812</v>
       </c>
       <c r="C195" t="n">
         <v>35.63000106811523</v>
@@ -4232,11 +4244,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>35.74297332763672</v>
+        <v>35.74297714233398</v>
       </c>
       <c r="C196" t="n">
         <v>41.33000183105469</v>
@@ -4261,11 +4273,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>35.49714660644531</v>
+        <v>35.49714279174805</v>
       </c>
       <c r="C197" t="n">
         <v>40.93000030517578</v>
@@ -4290,7 +4302,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -4319,11 +4331,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>30.26753616333008</v>
+        <v>30.26753807067871</v>
       </c>
       <c r="C199" t="n">
         <v>34.90000152587891</v>
@@ -4348,7 +4360,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -4377,11 +4389,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>34.04029083251953</v>
+        <v>34.04028701782227</v>
       </c>
       <c r="C201" t="n">
         <v>39.11000061035156</v>
@@ -4406,11 +4418,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>29.75805854797363</v>
+        <v>29.758056640625</v>
       </c>
       <c r="C202" t="n">
         <v>34.18999862670898</v>
@@ -4435,7 +4447,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -4464,11 +4476,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>41.02168273925781</v>
+        <v>41.02167892456055</v>
       </c>
       <c r="C204" t="n">
         <v>46.84999847412109</v>
@@ -4493,7 +4505,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -4522,11 +4534,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>39.03125381469727</v>
+        <v>39.0312614440918</v>
       </c>
       <c r="C206" t="n">
         <v>44.33000183105469</v>
@@ -4551,11 +4563,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>33.79246139526367</v>
+        <v>33.79245376586914</v>
       </c>
       <c r="C207" t="n">
         <v>38.38000106811523</v>
@@ -4580,11 +4592,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>31.7497730255127</v>
+        <v>31.74976539611816</v>
       </c>
       <c r="C208" t="n">
         <v>36.06000137329102</v>
@@ -4609,11 +4621,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>32.65579605102539</v>
+        <v>32.65579986572266</v>
       </c>
       <c r="C209" t="n">
         <v>36.84999847412109</v>
@@ -4638,11 +4650,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>28.1628589630127</v>
+        <v>28.16285514831543</v>
       </c>
       <c r="C210" t="n">
         <v>31.78000068664551</v>
@@ -4667,11 +4679,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>30.28083610534668</v>
+        <v>30.28083419799805</v>
       </c>
       <c r="C211" t="n">
         <v>34.16999816894531</v>
@@ -4696,11 +4708,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>36.11894226074219</v>
+        <v>36.11893463134766</v>
       </c>
       <c r="C212" t="n">
         <v>40.4900016784668</v>
@@ -4725,11 +4737,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>39.10729217529297</v>
+        <v>39.1072883605957</v>
       </c>
       <c r="C213" t="n">
         <v>43.84000015258789</v>
@@ -4754,11 +4766,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>36.6630859375</v>
+        <v>36.66308212280273</v>
       </c>
       <c r="C214" t="n">
         <v>41.09999847412109</v>
@@ -4783,7 +4795,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -4812,11 +4824,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>32.30014038085938</v>
+        <v>32.30014419555664</v>
       </c>
       <c r="C216" t="n">
         <v>36</v>
@@ -4841,11 +4853,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>32.19248199462891</v>
+        <v>32.19247817993164</v>
       </c>
       <c r="C217" t="n">
         <v>35.88000106811523</v>
@@ -4870,7 +4882,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -4899,11 +4911,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>26.94795608520508</v>
+        <v>26.94795417785645</v>
       </c>
       <c r="C219" t="n">
         <v>29.79000091552734</v>
@@ -4928,11 +4940,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>31.10005760192871</v>
+        <v>31.10006332397461</v>
       </c>
       <c r="C220" t="n">
         <v>34.38000106811523</v>
@@ -4957,11 +4969,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>28.66148948669434</v>
+        <v>28.66149139404297</v>
       </c>
       <c r="C221" t="n">
         <v>31.44000053405762</v>
@@ -4986,11 +4998,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>27.83191299438477</v>
+        <v>27.83191108703613</v>
       </c>
       <c r="C222" t="n">
         <v>30.53000068664551</v>
@@ -5015,7 +5027,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -5044,7 +5056,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -5073,11 +5085,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>26.17663764953613</v>
+        <v>26.17663955688477</v>
       </c>
       <c r="C225" t="n">
         <v>28.48999977111816</v>
@@ -5102,11 +5114,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>22.47386932373047</v>
+        <v>22.4738712310791</v>
       </c>
       <c r="C226" t="n">
         <v>24.45999908447266</v>
@@ -5131,11 +5143,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>21.90176010131836</v>
+        <v>21.90176200866699</v>
       </c>
       <c r="C227" t="n">
         <v>23.60000038146973</v>
@@ -5160,11 +5172,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>21.02012252807617</v>
+        <v>21.02011871337891</v>
       </c>
       <c r="C228" t="n">
         <v>22.64999961853027</v>
@@ -5189,11 +5201,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>21.42845916748047</v>
+        <v>21.42845726013184</v>
       </c>
       <c r="C229" t="n">
         <v>23.09000015258789</v>
@@ -5218,7 +5230,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -5247,11 +5259,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>19.41524314880371</v>
+        <v>19.41524505615234</v>
       </c>
       <c r="C231" t="n">
         <v>20.70000076293945</v>
@@ -5276,11 +5288,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>19.71538162231445</v>
+        <v>19.71538352966309</v>
       </c>
       <c r="C232" t="n">
         <v>21.02000045776367</v>
@@ -5305,11 +5317,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>14.81444358825684</v>
+        <v>14.81444454193115</v>
       </c>
       <c r="C233" t="n">
         <v>15.53999996185303</v>
@@ -5334,11 +5346,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>16.21581077575684</v>
+        <v>16.2158088684082</v>
       </c>
       <c r="C234" t="n">
         <v>17.01000022888184</v>
@@ -5363,11 +5375,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>17.4360466003418</v>
+        <v>17.43605041503906</v>
       </c>
       <c r="C235" t="n">
         <v>18.29000091552734</v>
@@ -5392,7 +5404,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -5421,7 +5433,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -5450,7 +5462,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -5479,11 +5491,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>22.13169288635254</v>
+        <v>22.13169097900391</v>
       </c>
       <c r="C239" t="n">
         <v>22.64999961853027</v>
@@ -5508,11 +5520,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>24.39860153198242</v>
+        <v>24.39860343933105</v>
       </c>
       <c r="C240" t="n">
         <v>24.96999931335449</v>
@@ -5537,7 +5549,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -5566,7 +5578,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -5595,7 +5607,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -5624,7 +5636,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -5653,7 +5665,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -5682,7 +5694,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -5711,7 +5723,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -5740,7 +5752,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -5769,7 +5781,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -5798,32 +5810,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>43.70000076293945</v>
+        <v>43.68000030517578</v>
       </c>
       <c r="C250" t="n">
-        <v>43.70000076293945</v>
+        <v>43.68000030517578</v>
       </c>
       <c r="D250" t="n">
-        <v>94744700</v>
+        <v>100880800</v>
       </c>
       <c r="E250" t="n">
         <v>4.73</v>
       </c>
       <c r="F250" t="n">
-        <v>9.238900795547453</v>
+        <v>9.234672368958938</v>
       </c>
       <c r="G250" t="n">
         <v>350351510</v>
       </c>
       <c r="H250" t="n">
-        <v>15310361254.29699</v>
+        <v>15303354063.7188</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2704275486068263</v>
+        <v>0.2879416732070029</v>
       </c>
     </row>
   </sheetData>
@@ -5855,75 +5867,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -5959,13 +5971,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -6001,13 +6013,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -6043,13 +6055,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -6076,7 +6088,7 @@
       <c r="I5" t="n">
         <v>-12.86</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K5" t="n">
@@ -6089,13 +6101,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -6122,7 +6134,7 @@
       <c r="I6" t="n">
         <v>0.01999999999999913</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K6" t="n">
@@ -6135,13 +6147,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -6168,7 +6180,7 @@
       <c r="I7" t="n">
         <v>1.859999999999999</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K7" t="n">
@@ -6181,13 +6193,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -6214,7 +6226,7 @@
       <c r="I8" t="n">
         <v>1.579999999999999</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K8" t="n">
@@ -6227,13 +6239,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -6260,7 +6272,7 @@
       <c r="I9" t="n">
         <v>2.59</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K9" t="n">
@@ -6273,13 +6285,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -6306,7 +6318,7 @@
       <c r="I10" t="n">
         <v>7</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K10" t="n">
@@ -6319,13 +6331,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -6352,7 +6364,7 @@
       <c r="I11" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K11" t="n">
@@ -6365,13 +6377,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -6398,7 +6410,7 @@
       <c r="I12" t="n">
         <v>10.47</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K12" t="n">
@@ -6411,13 +6423,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -6444,7 +6456,7 @@
       <c r="I13" t="n">
         <v>11.02</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K13" t="n">
@@ -6457,13 +6469,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -6490,7 +6502,7 @@
       <c r="I14" t="n">
         <v>6.369999999999999</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K14" t="n">
@@ -6503,13 +6515,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -6536,7 +6548,7 @@
       <c r="I15" t="n">
         <v>4.89</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K15" t="n">
@@ -6549,13 +6561,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -6582,7 +6594,7 @@
       <c r="I16" t="n">
         <v>5.1</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K16" t="n">
@@ -6595,13 +6607,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -6628,7 +6640,7 @@
       <c r="I17" t="n">
         <v>9.25</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="K17" t="n">
@@ -6641,13 +6653,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -6674,7 +6686,7 @@
       <c r="I18" t="n">
         <v>8.91</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K18" t="n">
@@ -6687,13 +6699,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -6720,7 +6732,7 @@
       <c r="I19" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K19" t="n">
@@ -6733,13 +6745,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6766,7 +6778,7 @@
       <c r="I20" t="n">
         <v>7.05</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="K20" t="n">
@@ -6779,13 +6791,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6812,7 +6824,7 @@
       <c r="I21" t="n">
         <v>2.27</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="K21" t="n">
@@ -6825,13 +6837,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6858,7 +6870,7 @@
       <c r="I22" t="n">
         <v>2.79</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="K22" t="n">
@@ -6871,13 +6883,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -6904,7 +6916,7 @@
       <c r="I23" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="K23" t="n">
@@ -6917,13 +6929,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -6950,7 +6962,7 @@
       <c r="I24" t="n">
         <v>4.17</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K24" t="n">
@@ -6963,13 +6975,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -6996,7 +7008,7 @@
       <c r="I25" t="n">
         <v>3.99</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="K25" t="n">
@@ -7009,13 +7021,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -7042,7 +7054,7 @@
       <c r="I26" t="n">
         <v>4.290000000000001</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="K26" t="n">
@@ -7055,13 +7067,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -7088,7 +7100,7 @@
       <c r="I27" t="n">
         <v>4.73</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="K27" t="n">
@@ -7125,52 +7137,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="C2" t="n">
@@ -7199,10 +7211,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C3" t="n">
@@ -7231,10 +7243,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="C4" t="n">
@@ -7263,10 +7275,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="C5" t="n">
@@ -7295,10 +7307,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C6" t="n">
@@ -7327,10 +7339,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C7" t="n">
@@ -7359,10 +7371,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C8" t="n">
@@ -7391,10 +7403,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C9" t="n">
@@ -7423,10 +7435,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C10" t="n">
@@ -7455,10 +7467,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C11" t="n">
@@ -7487,10 +7499,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C12" t="n">
@@ -7519,10 +7531,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="C13" t="n">
@@ -7551,10 +7563,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C14" t="n">
@@ -7583,10 +7595,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C15" t="n">
@@ -7615,10 +7627,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="C16" t="n">
@@ -7647,10 +7659,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="C17" t="n">
@@ -7679,10 +7691,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="C18" t="n">
@@ -7711,10 +7723,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="C19" t="n">
@@ -7743,10 +7755,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="C20" t="n">
@@ -7775,10 +7787,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="C21" t="n">
@@ -7807,10 +7819,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="C22" t="n">
@@ -7839,10 +7851,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C23" t="n">
@@ -7889,12 +7901,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/APA.xlsx
+++ b/salidas/empresas/APA.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>52.92543411254883</v>
+        <v>52.92544937133789</v>
       </c>
       <c r="C2" t="n">
         <v>75.52999877929688</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>46.89223861694336</v>
+        <v>46.89224243164062</v>
       </c>
       <c r="C3" t="n">
         <v>66.91999816894531</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>49.85017395019531</v>
+        <v>49.85016250610352</v>
       </c>
       <c r="C5" t="n">
         <v>71.04000091552734</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>45.5275764465332</v>
+        <v>45.52759552001953</v>
       </c>
       <c r="C6" t="n">
         <v>64.87999725341797</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>47.89238739013672</v>
+        <v>47.89239120483398</v>
       </c>
       <c r="C7" t="n">
         <v>68.25</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>49.52589797973633</v>
+        <v>49.52590560913086</v>
       </c>
       <c r="C8" t="n">
         <v>70.47000122070312</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>45.87838745117188</v>
+        <v>45.87839126586914</v>
       </c>
       <c r="C9" t="n">
         <v>65.27999877929688</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>44.41658782958984</v>
+        <v>44.41658020019531</v>
       </c>
       <c r="C10" t="n">
         <v>63.20000076293945</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>46.01251602172852</v>
+        <v>46.01251983642578</v>
       </c>
       <c r="C11" t="n">
         <v>65.31999969482422</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>49.2598991394043</v>
+        <v>49.25988006591797</v>
       </c>
       <c r="C12" t="n">
         <v>69.93000030517578</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>46.85076904296875</v>
+        <v>46.85077285766602</v>
       </c>
       <c r="C13" t="n">
         <v>66.51000213623047</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>51.51839065551758</v>
+        <v>51.51838684082031</v>
       </c>
       <c r="C14" t="n">
         <v>72.97000122070312</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>48.3342170715332</v>
+        <v>48.33420944213867</v>
       </c>
       <c r="C15" t="n">
         <v>68.45999908447266</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>49.91570663452148</v>
+        <v>49.91571044921875</v>
       </c>
       <c r="C16" t="n">
         <v>70.69999694824219</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>57.12575531005859</v>
+        <v>57.12577056884766</v>
       </c>
       <c r="C18" t="n">
         <v>80.75</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>57.72003173828125</v>
+        <v>57.72003936767578</v>
       </c>
       <c r="C19" t="n">
         <v>81.58999633789062</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>54.83560180664062</v>
+        <v>54.83559417724609</v>
       </c>
       <c r="C21" t="n">
         <v>77.37999725341797</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>63.82132339477539</v>
+        <v>63.82133102416992</v>
       </c>
       <c r="C22" t="n">
         <v>90.05999755859375</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>73.68097686767578</v>
+        <v>73.68096160888672</v>
       </c>
       <c r="C23" t="n">
         <v>103.8099975585938</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>68.69843292236328</v>
+        <v>68.69838714599609</v>
       </c>
       <c r="C24" t="n">
         <v>96.79000091552734</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>76.32843017578125</v>
+        <v>76.32839965820312</v>
       </c>
       <c r="C25" t="n">
         <v>107.5400009155273</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>67.78549957275391</v>
+        <v>67.78548431396484</v>
       </c>
       <c r="C26" t="n">
         <v>95.36000061035156</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>95.92720794677734</v>
+        <v>95.92723083496094</v>
       </c>
       <c r="C29" t="n">
         <v>134.6799926757812</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>95.485595703125</v>
+        <v>95.48564147949219</v>
       </c>
       <c r="C30" t="n">
         <v>134.0599975585938</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>80.00222778320312</v>
+        <v>80.00222015380859</v>
       </c>
       <c r="C32" t="n">
         <v>112.1699981689453</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>81.57848358154297</v>
+        <v>81.57845306396484</v>
       </c>
       <c r="C33" t="n">
         <v>114.379997253418</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>74.37490081787109</v>
+        <v>74.37489318847656</v>
       </c>
       <c r="C34" t="n">
         <v>104.2799987792969</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>58.83910369873047</v>
+        <v>58.83909225463867</v>
       </c>
       <c r="C35" t="n">
         <v>82.33000183105469</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>55.24432373046875</v>
+        <v>55.24431610107422</v>
       </c>
       <c r="C36" t="n">
         <v>77.30000305175781</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>53.26466369628906</v>
+        <v>53.2646369934082</v>
       </c>
       <c r="C37" t="n">
         <v>74.52999877929688</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>53.70869445800781</v>
+        <v>53.70869827270508</v>
       </c>
       <c r="C38" t="n">
         <v>75</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>42.31531524658203</v>
+        <v>42.3153076171875</v>
       </c>
       <c r="C39" t="n">
         <v>59.09000015258789</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>45.89587020874023</v>
+        <v>45.8958740234375</v>
       </c>
       <c r="C40" t="n">
         <v>64.08999633789062</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>52.28976440429688</v>
+        <v>52.28975296020508</v>
       </c>
       <c r="C41" t="n">
         <v>72.86000061035156</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>60.47124862670898</v>
+        <v>60.47121429443359</v>
       </c>
       <c r="C42" t="n">
         <v>84.26000213623047</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>51.78020858764648</v>
+        <v>51.78019332885742</v>
       </c>
       <c r="C43" t="n">
         <v>72.15000152587891</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>60.36869812011719</v>
+        <v>60.36867904663086</v>
       </c>
       <c r="C44" t="n">
         <v>83.94999694824219</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>61.08777618408203</v>
+        <v>61.0877799987793</v>
       </c>
       <c r="C45" t="n">
         <v>84.94999694824219</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>66.03520965576172</v>
+        <v>66.03525543212891</v>
       </c>
       <c r="C46" t="n">
         <v>91.83000183105469</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>67.77964782714844</v>
+        <v>67.77968597412109</v>
       </c>
       <c r="C47" t="n">
         <v>94.12000274658203</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>68.61504364013672</v>
+        <v>68.61503601074219</v>
       </c>
       <c r="C48" t="n">
         <v>95.27999877929688</v>
@@ -1391,7 +1391,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>74.29693603515625</v>
+        <v>74.29695892333984</v>
       </c>
       <c r="C49" t="n">
         <v>103.1699981689453</v>
@@ -1410,7 +1410,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>71.22689819335938</v>
+        <v>71.22686767578125</v>
       </c>
       <c r="C50" t="n">
         <v>98.76999664306641</v>
@@ -1429,7 +1429,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>74.73884582519531</v>
+        <v>74.73885345458984</v>
       </c>
       <c r="C51" t="n">
         <v>103.6399993896484</v>
@@ -1448,7 +1448,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>73.19558715820312</v>
+        <v>73.19559478759766</v>
       </c>
       <c r="C52" t="n">
         <v>101.5</v>
@@ -1486,7 +1486,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>64.66300201416016</v>
+        <v>64.6629638671875</v>
       </c>
       <c r="C54" t="n">
         <v>89.54000091552734</v>
@@ -1505,7 +1505,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>60.79937362670898</v>
+        <v>60.79938507080078</v>
       </c>
       <c r="C55" t="n">
         <v>84.19000244140625</v>
@@ -1524,7 +1524,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>69.14608001708984</v>
+        <v>69.14604949951172</v>
       </c>
       <c r="C56" t="n">
         <v>95.58000183105469</v>
@@ -1543,7 +1543,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>65.00078582763672</v>
+        <v>65.00075531005859</v>
       </c>
       <c r="C57" t="n">
         <v>89.84999847412109</v>
@@ -1562,7 +1562,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>70.72315979003906</v>
+        <v>70.72313690185547</v>
       </c>
       <c r="C58" t="n">
         <v>97.76000213623047</v>
@@ -1581,7 +1581,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>73.18889617919922</v>
+        <v>73.18890380859375</v>
       </c>
       <c r="C59" t="n">
         <v>101.0199966430664</v>
@@ -1600,7 +1600,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>77.98508453369141</v>
+        <v>77.98511505126953</v>
       </c>
       <c r="C60" t="n">
         <v>107.6399993896484</v>
@@ -1619,7 +1619,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>86.38204956054688</v>
+        <v>86.38203430175781</v>
       </c>
       <c r="C61" t="n">
         <v>119.2300033569336</v>
@@ -1657,7 +1657,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>90.39339447021484</v>
+        <v>90.39338684082031</v>
       </c>
       <c r="C63" t="n">
         <v>124.620002746582</v>
@@ -1676,7 +1676,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>94.96308898925781</v>
+        <v>94.96307373046875</v>
       </c>
       <c r="C64" t="n">
         <v>130.9199981689453</v>
@@ -1695,7 +1695,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>96.86038970947266</v>
+        <v>96.86034393310547</v>
       </c>
       <c r="C65" t="n">
         <v>133.3699951171875</v>
@@ -1714,7 +1714,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>90.49110412597656</v>
+        <v>90.49111938476562</v>
       </c>
       <c r="C66" t="n">
         <v>124.5999984741211</v>
@@ -1733,7 +1733,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>89.61234283447266</v>
+        <v>89.61235046386719</v>
       </c>
       <c r="C67" t="n">
         <v>123.3899993896484</v>
@@ -1752,7 +1752,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>89.95932769775391</v>
+        <v>89.95929718017578</v>
       </c>
       <c r="C68" t="n">
         <v>123.7200012207031</v>
@@ -1771,7 +1771,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>74.94429016113281</v>
+        <v>74.94429779052734</v>
       </c>
       <c r="C69" t="n">
         <v>103.0699996948242</v>
@@ -1790,7 +1790,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>58.34414291381836</v>
+        <v>58.34413528442383</v>
       </c>
       <c r="C70" t="n">
         <v>80.23999786376953</v>
@@ -1809,7 +1809,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>72.56340026855469</v>
+        <v>72.56336975097656</v>
       </c>
       <c r="C71" t="n">
         <v>99.62999725341797</v>
@@ -1828,7 +1828,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>72.42500305175781</v>
+        <v>72.42497253417969</v>
       </c>
       <c r="C72" t="n">
         <v>99.44000244140625</v>
@@ -1847,7 +1847,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>65.97201538085938</v>
+        <v>65.97202301025391</v>
       </c>
       <c r="C73" t="n">
         <v>90.58000183105469</v>
@@ -1885,7 +1885,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>78.73226165771484</v>
+        <v>78.73226928710938</v>
       </c>
       <c r="C75" t="n">
         <v>107.9300003051758</v>
@@ -1904,7 +1904,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>73.26849365234375</v>
+        <v>73.26848602294922</v>
       </c>
       <c r="C76" t="n">
         <v>100.4400024414062</v>
@@ -1942,7 +1942,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>59.47425079345703</v>
+        <v>59.47424697875977</v>
       </c>
       <c r="C78" t="n">
         <v>81.37999725341797</v>
@@ -1961,7 +1961,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>64.23188781738281</v>
+        <v>64.23192596435547</v>
       </c>
       <c r="C79" t="n">
         <v>87.88999938964844</v>
@@ -1980,7 +1980,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>63.06345367431641</v>
+        <v>63.06346130371094</v>
       </c>
       <c r="C80" t="n">
         <v>86.12000274658203</v>
@@ -1999,7 +1999,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>62.79251480102539</v>
+        <v>62.79249572753906</v>
       </c>
       <c r="C81" t="n">
         <v>85.75</v>
@@ -2037,7 +2037,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>60.69001770019531</v>
+        <v>60.68999481201172</v>
       </c>
       <c r="C83" t="n">
         <v>82.72000122070312</v>
@@ -2056,7 +2056,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>56.55936813354492</v>
+        <v>56.55938339233398</v>
       </c>
       <c r="C84" t="n">
         <v>77.08999633789062</v>
@@ -2075,7 +2075,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>57.59389495849609</v>
+        <v>57.5938606262207</v>
       </c>
       <c r="C85" t="n">
         <v>78.5</v>
@@ -2094,7 +2094,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>61.58256149291992</v>
+        <v>61.58256530761719</v>
       </c>
       <c r="C86" t="n">
         <v>83.76000213623047</v>
@@ -2113,7 +2113,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>54.60525512695312</v>
+        <v>54.60524368286133</v>
       </c>
       <c r="C87" t="n">
         <v>74.26999664306641</v>
@@ -2132,7 +2132,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>56.73006439208984</v>
+        <v>56.73006057739258</v>
       </c>
       <c r="C88" t="n">
         <v>77.16000366210938</v>
@@ -2151,7 +2151,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>54.47097396850586</v>
+        <v>54.47100067138672</v>
       </c>
       <c r="C89" t="n">
         <v>73.87999725341797</v>
@@ -2170,7 +2170,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>60.55363464355469</v>
+        <v>60.55362701416016</v>
       </c>
       <c r="C90" t="n">
         <v>82.12999725341797</v>
@@ -2189,7 +2189,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>61.80702972412109</v>
+        <v>61.8070182800293</v>
       </c>
       <c r="C91" t="n">
         <v>83.83000183105469</v>
@@ -2208,7 +2208,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>59.3112907409668</v>
+        <v>59.31129455566406</v>
       </c>
       <c r="C92" t="n">
         <v>80.25</v>
@@ -2227,7 +2227,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>63.32450103759766</v>
+        <v>63.32452011108398</v>
       </c>
       <c r="C93" t="n">
         <v>85.68000030517578</v>
@@ -2246,7 +2246,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>62.92541122436523</v>
+        <v>62.92544555664062</v>
       </c>
       <c r="C94" t="n">
         <v>85.13999938964844</v>
@@ -2265,7 +2265,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>65.77568054199219</v>
+        <v>65.77568817138672</v>
       </c>
       <c r="C95" t="n">
         <v>88.80000305175781</v>
@@ -2303,7 +2303,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>63.65723419189453</v>
+        <v>63.6572151184082</v>
       </c>
       <c r="C97" t="n">
         <v>85.94000244140625</v>
@@ -2322,7 +2322,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>59.58869552612305</v>
+        <v>59.58868789672852</v>
       </c>
       <c r="C98" t="n">
         <v>80.26000213623047</v>
@@ -2341,7 +2341,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>58.86854934692383</v>
+        <v>58.86853790283203</v>
       </c>
       <c r="C99" t="n">
         <v>79.29000091552734</v>
@@ -2360,7 +2360,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>61.58585357666016</v>
+        <v>61.58588027954102</v>
       </c>
       <c r="C100" t="n">
         <v>82.94999694824219</v>
@@ -2398,7 +2398,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>69.41698455810547</v>
+        <v>69.41699981689453</v>
       </c>
       <c r="C102" t="n">
         <v>93.22000122070312</v>
@@ -2474,7 +2474,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>70.07814025878906</v>
+        <v>70.078125</v>
       </c>
       <c r="C106" t="n">
         <v>93.87000274658203</v>
@@ -2512,7 +2512,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>48.01079177856445</v>
+        <v>48.01079940795898</v>
       </c>
       <c r="C108" t="n">
         <v>64.08999633789062</v>
@@ -2531,7 +2531,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>46.94704437255859</v>
+        <v>46.94704818725586</v>
       </c>
       <c r="C109" t="n">
         <v>62.66999816894531</v>
@@ -2550,7 +2550,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>47.0611572265625</v>
+        <v>47.06113052368164</v>
       </c>
       <c r="C110" t="n">
         <v>62.56999969482422</v>
@@ -2569,7 +2569,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>49.52061462402344</v>
+        <v>49.52062225341797</v>
       </c>
       <c r="C111" t="n">
         <v>65.83999633789062</v>
@@ -2588,7 +2588,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>45.37636947631836</v>
+        <v>45.37637710571289</v>
       </c>
       <c r="C112" t="n">
         <v>60.33000183105469</v>
@@ -2607,7 +2607,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>51.6295051574707</v>
+        <v>51.62949371337891</v>
       </c>
       <c r="C113" t="n">
         <v>68.40000152587891</v>
@@ -2626,7 +2626,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>45.16825485229492</v>
+        <v>45.16825103759766</v>
       </c>
       <c r="C114" t="n">
         <v>59.84000015258789</v>
@@ -2664,7 +2664,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>34.78765487670898</v>
+        <v>34.78764724731445</v>
       </c>
       <c r="C116" t="n">
         <v>45.86000061035156</v>
@@ -2683,7 +2683,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>34.31734085083008</v>
+        <v>34.31734848022461</v>
       </c>
       <c r="C117" t="n">
         <v>45.2400016784668</v>
@@ -2702,7 +2702,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>29.70529174804688</v>
+        <v>29.70528030395508</v>
       </c>
       <c r="C118" t="n">
         <v>39.15999984741211</v>
@@ -2721,7 +2721,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>35.94927978515625</v>
+        <v>35.94928741455078</v>
       </c>
       <c r="C119" t="n">
         <v>47.13000106811523</v>
@@ -2778,7 +2778,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>32.6851806640625</v>
+        <v>32.68516159057617</v>
       </c>
       <c r="C122" t="n">
         <v>42.54000091552734</v>
@@ -2797,7 +2797,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>29.41204452514648</v>
+        <v>29.41204261779785</v>
       </c>
       <c r="C123" t="n">
         <v>38.27999877929688</v>
@@ -2816,7 +2816,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>37.50265502929688</v>
+        <v>37.50266265869141</v>
       </c>
       <c r="C124" t="n">
         <v>48.81000137329102</v>
@@ -2835,7 +2835,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>41.98845672607422</v>
+        <v>41.98846054077148</v>
       </c>
       <c r="C125" t="n">
         <v>54.40000152587891</v>
@@ -2854,7 +2854,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>44.10332489013672</v>
+        <v>44.10330963134766</v>
       </c>
       <c r="C126" t="n">
         <v>57.13999938964844</v>
@@ -2873,7 +2873,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>42.96871185302734</v>
+        <v>42.96871948242188</v>
       </c>
       <c r="C127" t="n">
         <v>55.66999816894531</v>
@@ -2892,7 +2892,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>40.70662307739258</v>
+        <v>40.70660781860352</v>
       </c>
       <c r="C128" t="n">
         <v>52.5</v>
@@ -2911,7 +2911,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>38.53560638427734</v>
+        <v>38.53559112548828</v>
       </c>
       <c r="C129" t="n">
         <v>49.70000076293945</v>
@@ -2930,7 +2930,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>49.52250671386719</v>
+        <v>49.52249145507812</v>
       </c>
       <c r="C130" t="n">
         <v>63.86999893188477</v>
@@ -2949,7 +2949,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>46.30289840698242</v>
+        <v>46.30289077758789</v>
       </c>
       <c r="C131" t="n">
         <v>59.47999954223633</v>
@@ -2968,7 +2968,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>51.33953857421875</v>
+        <v>51.33954238891602</v>
       </c>
       <c r="C132" t="n">
         <v>65.94999694824219</v>
@@ -2987,7 +2987,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>49.4089469909668</v>
+        <v>49.40895843505859</v>
       </c>
       <c r="C133" t="n">
         <v>63.47000122070312</v>
@@ -3006,7 +3006,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>46.75281143188477</v>
+        <v>46.7528076171875</v>
       </c>
       <c r="C134" t="n">
         <v>59.81999969482422</v>
@@ -3025,7 +3025,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>41.10214233398438</v>
+        <v>41.10213470458984</v>
       </c>
       <c r="C135" t="n">
         <v>52.59000015258789</v>
@@ -3044,7 +3044,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>40.16426467895508</v>
+        <v>40.16427230834961</v>
       </c>
       <c r="C136" t="n">
         <v>51.38999938964844</v>
@@ -3063,7 +3063,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>38.20430755615234</v>
+        <v>38.20431518554688</v>
       </c>
       <c r="C137" t="n">
         <v>48.63999938964844</v>
@@ -3101,7 +3101,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>37.64664077758789</v>
+        <v>37.64663314819336</v>
       </c>
       <c r="C139" t="n">
         <v>47.93000030517578</v>
@@ -3120,7 +3120,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>39.06872177124023</v>
+        <v>39.06871032714844</v>
       </c>
       <c r="C140" t="n">
         <v>49.47999954223633</v>
@@ -3139,7 +3139,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>30.66752433776855</v>
+        <v>30.66751670837402</v>
       </c>
       <c r="C141" t="n">
         <v>38.84000015258789</v>
@@ -3158,7 +3158,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>36.16304397583008</v>
+        <v>36.16304016113281</v>
       </c>
       <c r="C142" t="n">
         <v>45.79999923706055</v>
@@ -3234,7 +3234,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>35.83193206787109</v>
+        <v>35.83194732666016</v>
       </c>
       <c r="C146" t="n">
         <v>44.86999893188477</v>
@@ -3253,7 +3253,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>27.271240234375</v>
+        <v>27.2712516784668</v>
       </c>
       <c r="C147" t="n">
         <v>34.15000152587891</v>
@@ -3272,7 +3272,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>30.72905921936035</v>
+        <v>30.72906494140625</v>
       </c>
       <c r="C148" t="n">
         <v>38.47999954223633</v>
@@ -3291,7 +3291,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>32.89720916748047</v>
+        <v>32.89720153808594</v>
       </c>
       <c r="C149" t="n">
         <v>40.95000076293945</v>
@@ -3310,7 +3310,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>32.13402557373047</v>
+        <v>32.1340217590332</v>
       </c>
       <c r="C150" t="n">
         <v>40</v>
@@ -3329,7 +3329,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>37.55665588378906</v>
+        <v>37.55663681030273</v>
       </c>
       <c r="C151" t="n">
         <v>46.75</v>
@@ -3348,7 +3348,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>37.16267013549805</v>
+        <v>37.16268157958984</v>
       </c>
       <c r="C152" t="n">
         <v>46</v>
@@ -3367,7 +3367,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>35.40956497192383</v>
+        <v>35.40957260131836</v>
       </c>
       <c r="C153" t="n">
         <v>43.83000183105469</v>
@@ -3386,7 +3386,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>38.51183319091797</v>
+        <v>38.51183700561523</v>
       </c>
       <c r="C154" t="n">
         <v>47.66999816894531</v>
@@ -3405,7 +3405,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>30.74383735656738</v>
+        <v>30.74382972717285</v>
       </c>
       <c r="C155" t="n">
         <v>37.83000183105469</v>
@@ -3424,7 +3424,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>28.54958724975586</v>
+        <v>28.54958915710449</v>
       </c>
       <c r="C156" t="n">
         <v>35.13000106811523</v>
@@ -3443,7 +3443,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>21.33295249938965</v>
+        <v>21.33294677734375</v>
       </c>
       <c r="C157" t="n">
         <v>26.25</v>
@@ -3462,7 +3462,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>26.88437843322754</v>
+        <v>26.88436698913574</v>
       </c>
       <c r="C158" t="n">
         <v>32.81999969482422</v>
@@ -3481,7 +3481,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>27.17927169799805</v>
+        <v>27.17926979064941</v>
       </c>
       <c r="C159" t="n">
         <v>33.18000030517578</v>
@@ -3500,7 +3500,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>28.3916015625</v>
+        <v>28.39160919189453</v>
       </c>
       <c r="C160" t="n">
         <v>34.65999984741211</v>
@@ -3538,7 +3538,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>21.50104522705078</v>
+        <v>21.50104331970215</v>
       </c>
       <c r="C162" t="n">
         <v>26.06999969482422</v>
@@ -3557,7 +3557,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>23.89280128479004</v>
+        <v>23.89280700683594</v>
       </c>
       <c r="C163" t="n">
         <v>28.96999931335449</v>
@@ -3614,7 +3614,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>21.33995819091797</v>
+        <v>21.3399543762207</v>
       </c>
       <c r="C166" t="n">
         <v>25.60000038146973</v>
@@ -3633,7 +3633,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>18.2590217590332</v>
+        <v>18.2590274810791</v>
       </c>
       <c r="C167" t="n">
         <v>21.65999984741211</v>
@@ -3671,7 +3671,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>21.57194709777832</v>
+        <v>21.57195091247559</v>
       </c>
       <c r="C169" t="n">
         <v>25.59000015258789</v>
@@ -3690,7 +3690,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>23.30984115600586</v>
+        <v>23.30984687805176</v>
       </c>
       <c r="C170" t="n">
         <v>27.44000053405762</v>
@@ -3728,7 +3728,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>3.550843238830566</v>
+        <v>3.550842523574829</v>
       </c>
       <c r="C172" t="n">
         <v>4.179999828338623</v>
@@ -3747,7 +3747,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>11.14410495758057</v>
+        <v>11.14410400390625</v>
       </c>
       <c r="C173" t="n">
         <v>13.07999992370605</v>
@@ -3766,7 +3766,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>9.193037986755371</v>
+        <v>9.193035125732422</v>
       </c>
       <c r="C174" t="n">
         <v>10.78999996185303</v>
@@ -3785,7 +3785,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>11.50194358825684</v>
+        <v>11.50194549560547</v>
       </c>
       <c r="C175" t="n">
         <v>13.5</v>
@@ -3804,7 +3804,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>13.10222148895264</v>
+        <v>13.102219581604</v>
       </c>
       <c r="C176" t="n">
         <v>15.35000038146973</v>
@@ -3823,7 +3823,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>12.6327600479126</v>
+        <v>12.63275814056396</v>
       </c>
       <c r="C177" t="n">
         <v>14.80000019073486</v>
@@ -3842,7 +3842,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>8.083256721496582</v>
+        <v>8.083258628845215</v>
       </c>
       <c r="C178" t="n">
         <v>9.470000267028809</v>
@@ -3861,7 +3861,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>7.103066444396973</v>
+        <v>7.103065013885498</v>
       </c>
       <c r="C179" t="n">
         <v>8.300000190734863</v>
@@ -3880,7 +3880,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>11.03114986419678</v>
+        <v>11.03114700317383</v>
       </c>
       <c r="C180" t="n">
         <v>12.89000034332275</v>
@@ -3899,7 +3899,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>12.1436767578125</v>
+        <v>12.14367580413818</v>
       </c>
       <c r="C181" t="n">
         <v>14.1899995803833</v>
@@ -3918,7 +3918,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>12.23821067810059</v>
+        <v>12.23821258544922</v>
       </c>
       <c r="C182" t="n">
         <v>14.27999973297119</v>
@@ -3937,7 +3937,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>16.90896034240723</v>
+        <v>16.90895462036133</v>
       </c>
       <c r="C183" t="n">
         <v>19.72999954223633</v>
@@ -3956,7 +3956,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>15.34061336517334</v>
+        <v>15.34061717987061</v>
       </c>
       <c r="C184" t="n">
         <v>17.89999961853027</v>
@@ -3975,7 +3975,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>17.16559791564941</v>
+        <v>17.16559600830078</v>
       </c>
       <c r="C185" t="n">
         <v>20</v>
@@ -3994,7 +3994,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>17.85222053527832</v>
+        <v>17.85221290588379</v>
       </c>
       <c r="C186" t="n">
         <v>20.79999923706055</v>
@@ -4019,7 +4019,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>18.56459426879883</v>
+        <v>18.5645866394043</v>
       </c>
       <c r="C187" t="n">
         <v>21.6299991607666</v>
@@ -4044,7 +4044,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>16.11568832397461</v>
+        <v>16.11569404602051</v>
       </c>
       <c r="C188" t="n">
         <v>18.75</v>
@@ -4069,7 +4069,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>16.74312400817871</v>
+        <v>16.74312782287598</v>
       </c>
       <c r="C189" t="n">
         <v>19.47999954223633</v>
@@ -4094,7 +4094,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>18.41916275024414</v>
+        <v>18.41915702819824</v>
       </c>
       <c r="C190" t="n">
         <v>21.43000030517578</v>
@@ -4119,7 +4119,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>22.57940673828125</v>
+        <v>22.57940864562988</v>
       </c>
       <c r="C191" t="n">
         <v>26.20999908447266</v>
@@ -4144,7 +4144,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>22.20036125183105</v>
+        <v>22.20035552978516</v>
       </c>
       <c r="C192" t="n">
         <v>25.77000045776367</v>
@@ -4194,7 +4194,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>28.72064781188965</v>
+        <v>28.72064399719238</v>
       </c>
       <c r="C194" t="n">
         <v>33.20999908447266</v>
@@ -4219,7 +4219,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>30.81350708007812</v>
+        <v>30.81351280212402</v>
       </c>
       <c r="C195" t="n">
         <v>35.63000106811523</v>
@@ -4248,7 +4248,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>35.74297714233398</v>
+        <v>35.74298477172852</v>
       </c>
       <c r="C196" t="n">
         <v>41.33000183105469</v>
@@ -4277,7 +4277,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>35.49714279174805</v>
+        <v>35.49714660644531</v>
       </c>
       <c r="C197" t="n">
         <v>40.93000030517578</v>
@@ -4306,7 +4306,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>40.77010726928711</v>
+        <v>40.77011489868164</v>
       </c>
       <c r="C198" t="n">
         <v>47.0099983215332</v>
@@ -4335,7 +4335,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>30.26753807067871</v>
+        <v>30.26753997802734</v>
       </c>
       <c r="C199" t="n">
         <v>34.90000152587891</v>
@@ -4364,7 +4364,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>32.35177230834961</v>
+        <v>32.35176467895508</v>
       </c>
       <c r="C200" t="n">
         <v>37.16999816894531</v>
@@ -4393,7 +4393,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>34.04028701782227</v>
+        <v>34.04029083251953</v>
       </c>
       <c r="C201" t="n">
         <v>39.11000061035156</v>
@@ -4451,7 +4451,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>39.80459976196289</v>
+        <v>39.80461502075195</v>
       </c>
       <c r="C203" t="n">
         <v>45.45999908447266</v>
@@ -4480,7 +4480,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>41.02167892456055</v>
+        <v>41.02168273925781</v>
       </c>
       <c r="C204" t="n">
         <v>46.84999847412109</v>
@@ -4538,7 +4538,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>39.0312614440918</v>
+        <v>39.03125</v>
       </c>
       <c r="C206" t="n">
         <v>44.33000183105469</v>
@@ -4567,7 +4567,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>33.79245376586914</v>
+        <v>33.79244613647461</v>
       </c>
       <c r="C207" t="n">
         <v>38.38000106811523</v>
@@ -4625,7 +4625,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>32.65579986572266</v>
+        <v>32.65579605102539</v>
       </c>
       <c r="C209" t="n">
         <v>36.84999847412109</v>
@@ -4654,7 +4654,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>28.16285514831543</v>
+        <v>28.16285705566406</v>
       </c>
       <c r="C210" t="n">
         <v>31.78000068664551</v>
@@ -4712,7 +4712,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>36.11893463134766</v>
+        <v>36.11893844604492</v>
       </c>
       <c r="C212" t="n">
         <v>40.4900016784668</v>
@@ -4770,7 +4770,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>36.66308212280273</v>
+        <v>36.6630859375</v>
       </c>
       <c r="C214" t="n">
         <v>41.09999847412109</v>
@@ -4799,7 +4799,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>35.63782119750977</v>
+        <v>35.6378288269043</v>
       </c>
       <c r="C215" t="n">
         <v>39.72000122070312</v>
@@ -4828,7 +4828,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>32.30014419555664</v>
+        <v>32.30014801025391</v>
       </c>
       <c r="C216" t="n">
         <v>36</v>
@@ -4857,7 +4857,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>32.19247817993164</v>
+        <v>32.19247436523438</v>
       </c>
       <c r="C217" t="n">
         <v>35.88000106811523</v>
@@ -4886,7 +4886,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>28.34103584289551</v>
+        <v>28.34103775024414</v>
       </c>
       <c r="C218" t="n">
         <v>31.32999992370605</v>
@@ -4915,7 +4915,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>26.94795417785645</v>
+        <v>26.94795799255371</v>
       </c>
       <c r="C219" t="n">
         <v>29.79000091552734</v>
@@ -4973,7 +4973,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>28.66149139404297</v>
+        <v>28.66148948669434</v>
       </c>
       <c r="C221" t="n">
         <v>31.44000053405762</v>
@@ -5031,7 +5031,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>26.8382396697998</v>
+        <v>26.83823776245117</v>
       </c>
       <c r="C223" t="n">
         <v>29.44000053405762</v>
@@ -5089,7 +5089,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>26.17663955688477</v>
+        <v>26.17663764953613</v>
       </c>
       <c r="C225" t="n">
         <v>28.48999977111816</v>
@@ -5118,7 +5118,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>22.4738712310791</v>
+        <v>22.47386741638184</v>
       </c>
       <c r="C226" t="n">
         <v>24.45999908447266</v>
@@ -5205,7 +5205,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>21.42845726013184</v>
+        <v>21.42845916748047</v>
       </c>
       <c r="C229" t="n">
         <v>23.09000015258789</v>
@@ -5292,7 +5292,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>19.71538352966309</v>
+        <v>19.71538543701172</v>
       </c>
       <c r="C232" t="n">
         <v>21.02000045776367</v>
@@ -5321,7 +5321,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>14.81444454193115</v>
+        <v>14.81444358825684</v>
       </c>
       <c r="C233" t="n">
         <v>15.53999996185303</v>
@@ -5350,7 +5350,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>16.2158088684082</v>
+        <v>16.21581268310547</v>
       </c>
       <c r="C234" t="n">
         <v>17.01000022888184</v>
@@ -5379,7 +5379,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>17.43605041503906</v>
+        <v>17.43604850769043</v>
       </c>
       <c r="C235" t="n">
         <v>18.29000091552734</v>
@@ -5495,7 +5495,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>22.13169097900391</v>
+        <v>22.13169288635254</v>
       </c>
       <c r="C239" t="n">
         <v>22.64999961853027</v>
@@ -5524,7 +5524,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>24.39860343933105</v>
+        <v>24.39860153198242</v>
       </c>
       <c r="C240" t="n">
         <v>24.96999931335449</v>
